--- a/data/trans_bre/IP04D$aparatos-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Estudios-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 10,86</t>
+          <t>-12,2; 9,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 10,96</t>
+          <t>-14,95; 11,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 16,07</t>
+          <t>-24,61; 15,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 17,16</t>
+          <t>-15,91; 14,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 18,56</t>
+          <t>-20,55; 19,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 26,31</t>
+          <t>-34,3; 26,9</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 8,99</t>
+          <t>-1,05; 8,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 5,05</t>
+          <t>-5,71; 4,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 12,39</t>
+          <t>-1,46; 12,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 14,54</t>
+          <t>-1,58; 14,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 9,79</t>
+          <t>-9,9; 9,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 20,78</t>
+          <t>-2,22; 20,34</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 9,8</t>
+          <t>-7,73; 10,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 6,51</t>
+          <t>-10,53; 7,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 11,24</t>
+          <t>-7,09; 11,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 21,45</t>
+          <t>-14,42; 24,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 16,85</t>
+          <t>-22,93; 20,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 30,74</t>
+          <t>-15,61; 32,37</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 6,89</t>
+          <t>-1,45; 6,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 3,28</t>
+          <t>-5,33; 3,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 10,34</t>
+          <t>-0,74; 10,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 11,36</t>
+          <t>-2,18; 11,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 6,34</t>
+          <t>-9,54; 6,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 18,61</t>
+          <t>-1,31; 17,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$aparatos-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Estudios-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 9,4</t>
+          <t>-12,33; 10,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 11,32</t>
+          <t>-17,2; 12,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 15,95</t>
+          <t>-26,85; 15,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 14,37</t>
+          <t>-16,08; 15,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 19,7</t>
+          <t>-23,34; 20,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,3; 26,9</t>
+          <t>-36,62; 25,26</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 8,9</t>
+          <t>-1,1; 9,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 4,7</t>
+          <t>-5,38; 5,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 12,0</t>
+          <t>-1,58; 12,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 14,48</t>
+          <t>-1,66; 14,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 9,13</t>
+          <t>-9,42; 9,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 20,34</t>
+          <t>-2,32; 21,84</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 10,59</t>
+          <t>-8,54; 9,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 7,44</t>
+          <t>-10,76; 6,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 11,43</t>
+          <t>-8,27; 11,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 24,23</t>
+          <t>-16,16; 19,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 20,46</t>
+          <t>-22,82; 17,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 32,37</t>
+          <t>-18,21; 32,55</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 6,98</t>
+          <t>-1,84; 6,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 3,13</t>
+          <t>-5,19; 3,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 10,11</t>
+          <t>-1,47; 10,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 11,79</t>
+          <t>-2,89; 11,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 6,3</t>
+          <t>-9,56; 6,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 17,83</t>
+          <t>-2,4; 18,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$aparatos-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Estudios-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>6,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,17%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 10,43</t>
+          <t>-11,42; 10,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 12,12</t>
+          <t>-16,26; 10,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 15,31</t>
+          <t>-9,55; 22,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 15,35</t>
+          <t>-15,16; 17,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 20,9</t>
+          <t>-22,89; 18,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 25,26</t>
+          <t>-12,72; 37,54</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,89</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,27</t>
+          <t>-1,15; 8,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 5,01</t>
+          <t>-5,53; 5,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 12,81</t>
+          <t>-4,16; 8,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 14,89</t>
+          <t>-1,61; 14,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 9,99</t>
+          <t>-9,66; 9,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 21,84</t>
+          <t>-5,99; 14,0</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 9,0</t>
+          <t>-7,81; 9,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 6,7</t>
+          <t>-10,38; 6,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 11,96</t>
+          <t>-8,1; 10,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 19,93</t>
+          <t>-14,44; 21,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 17,0</t>
+          <t>-22,09; 16,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 32,55</t>
+          <t>-17,42; 26,2</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,62</t>
+          <t>-1,16; 6,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 3,16</t>
+          <t>-5,23; 3,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 10,63</t>
+          <t>-2,21; 7,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 11,0</t>
+          <t>-2,08; 11,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 6,12</t>
+          <t>-9,61; 6,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 18,68</t>
+          <t>-3,57; 13,23</t>
         </is>
       </c>
     </row>
